--- a/artfynd/A 39172-2021 artfynd.xlsx
+++ b/artfynd/A 39172-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39172-2021 artfynd.xlsx
+++ b/artfynd/A 39172-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80675863</v>
+        <v>80675864</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508848.9586752065</v>
+        <v>508826</v>
       </c>
       <c r="R2" t="n">
-        <v>6945902.954171105</v>
+        <v>6945731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2019-05-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80675864</v>
+        <v>80675865</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508825.9293413877</v>
+        <v>508612</v>
       </c>
       <c r="R3" t="n">
-        <v>6945730.884039887</v>
+        <v>6946006</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +867,9 @@
           <t>2019-05-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-05-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -947,15 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80675865</v>
+        <v>115162621</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,14 +951,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömmingstjärnen, Jmt</t>
+          <t>Strömmingstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508611.9637759115</v>
+        <v>508831</v>
       </c>
       <c r="R4" t="n">
-        <v>6946005.805360612</v>
+        <v>6945571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,22 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,38 +1003,260 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>80675863</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strömmingstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508849</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6945903</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-05-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-05-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Sven Bengtsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Sven Bengtsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>80675858</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508928</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6945990</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39172-2021 artfynd.xlsx
+++ b/artfynd/A 39172-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675858</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675864</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675865</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115162621</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,8 +1282,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>